--- a/scenarios/S02_process_innovation/deliverables/배부기준_물동추적_시트.xlsx
+++ b/scenarios/S02_process_innovation/deliverables/배부기준_물동추적_시트.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배부기준" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="법인간비용배분" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="원가추적번호마스터" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,7 +467,6 @@
           <t>전 생산법인</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -516,7 +516,6 @@
           <t>전 법인</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -539,7 +538,6 @@
           <t>R&amp;D 참여법인</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -562,7 +560,6 @@
           <t>전 법인</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -585,7 +582,6 @@
           <t>물류 참여법인</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -945,4 +941,370 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>req_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>요청자</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>영향 산출물</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>변경유형</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DA점수</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>위키 커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-20250308-총원가-원가추적-전환</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:14:11.582+09:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PI팀 이과장</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bench:S02:B00000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>승인된 변경사항을 관련 설계서·시스템 요구사항·테스트 시나리오에 반영하고, 삼성방식 총원가 산식·통제·컴플라이언스·단계적 전환 및 롤백 기준은 후속 확정 과제로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>수작업 관리연결결산을 폐지하고 전 법인의 물동·간접비·법인간 비용을 원가추적번호 기반으로 실시간 관리하는 총원가 체계 설계</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>원가관리 업무 프로세스 정의서; 원가추적번호 설계서; 간접비 배부 및 법인간 비용배분 설계서; 실시간 원가 추적 시스템 요구사항; 테스트 시나리오</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/49cfed897a4753b1f533242ad6b60a0ebac0aa56</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-20250308-총원가-원가추적-전환-승인-실행-반영-v2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:32:08.856+09:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PI팀 이과장</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bench:S02:B00001</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>승인 페이로드와 실행 결과 초안을 Wiki에 반영하고 5개 영향 산출물의 갱신을 승인한다. 총원가 산식·컴플라이언스·데이터 정합성·단계적 전환·롤백 기준은 후속 확정 과제로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>수작업 관리연결결산 폐지, 삼성방식 총원가 기반 표준 프로세스 전환, 원가추적번호·간접비 배부·법인간 비용배분·실시간 원가관리·검증 및 이관 테스트를 5개 산출물에 반영</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>원가관리 업무 프로세스 정의서; 원가추적번호 설계서; 간접비 배부 및 법인간 비용배분 설계서; 실시간 원가 추적 시스템 요구사항; 테스트 시나리오</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/3acea49c31633acfb90df13adf7afc10327ac1fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20260725-총원가-원가추적-전환-승인-실행-반영</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:28:36.891+09:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PI팀 이과장</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bench:S02:B00010</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>수작업 관리연결결산 폐지와 원가추적번호 기반 실시간 총원가 관리 전환 및 6개 영향 산출물의 갱신을 승인한다. 공식 산식·배부 기준·법인간 거래 통제·데이터 소유권·대사 기준·단계적 전환·롤백 조건은 후속 확정한다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>전사 총원가·원가추적번호 기반 실시간 원가관리 전환을 설계에 반영했으며 산식·배부·법인간 거래 통제와 단계적 전환 기준 확정이 필요함</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>원가관리 업무 프로세스 정의서; 원가추적번호 설계서; 간접비 배부 및 법인간 비용배분 설계서; 실시간 원가 추적 시스템 요구사항; 테스트 시나리오; 기성 산출물</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/540d22a46f4e8cf40730f28f9ee06c26a74bfd11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-20250308-총원가-원가추적-전환-승인-실행</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-31T13:25:12.589Z</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PI팀 이과장</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bench:S02:B00100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>승인 페이로드에 따라 7개 영향 산출물과 Wiki를 갱신 대상으로 확정하고, 총원가 산식·배부·법인간 거래·컴플라이언스·단계적 전환 및 롤백 기준은 후속 확정 과제로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>수작업 관리연결결산을 폐지하고 원가추적번호 기반 전사 총원가·실시간 원가관리 체계를 관련 산출물과 Wiki에 반영한다.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>원가관리 업무 프로세스 정의서; 원가추적번호 설계서; 간접비 배부 및 법인간 비용배분 설계서; 실시간 원가 추적 시스템 요구사항; 테스트 시나리오; 요구사항 추적표; 설계서 및 보고 장표</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>modify; add; add; add; add; modify; modify</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/212b0f04225118940f97f6349a1890d454782fca</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-20250308-총원가-원가추적-전환-실행반영</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:21:23.089+09:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PI팀 이과장</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bench:S02:B01000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>승인 페이로드와 실행 결과 초안을 반영하고 5종 기성 산출물의 갱신을 승인한다. 삼성방식 총원가 산식, 데이터 거버넌스, 컴플라이언스, 전환·병행운영·롤백 기준은 후속 확정·검증한다.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>수작업 관리연결결산을 폐지하고 원가추적번호 기반 실시간 총원가 체계로 전환하며, 전 법인 물동·원가·간접비·법인간 비용·이전가격 차이·미실현이익 제거 및 검증·대사 절차를 5종 산출물에 반영</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>원가관리 업무 프로세스 정의서; 원가추적번호 설계서; 간접비 배부 및 법인간 비용배분 설계서; 실시간 원가 추적 시스템 요구사항; 테스트 시나리오</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/4f89c59552d49bf77492a5784bc73c699a5891f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-20250308-총원가-원가추적-전환-승인</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:17:31.610+09:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PI팀 이과장</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bench:S02:B10000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>승인 페이로드와 실행 결과 초안을 반영한다. 핵심 산식·컴플라이언스 통제·시스템 책임경계·단계적 전환 및 롤백 기준은 후속 확정·영향평가·파일럿 검증 과제로 관리한다.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>수작업 관리연결결산 폐지, 원가추적번호 기반 전 법인 물동·직접원가·간접비·법인간 비용 추적, 실시간 집계·통제·이관·대사·롤백 시나리오 반영</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>원가관리 업무 프로세스 정의서; 원가추적번호 설계서; 간접비 배부 및 법인간 비용배분 설계서; 실시간 원가 추적 시스템 요구사항; 테스트 시나리오</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>modify/add</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/d9f80ac42fb78f0ce93785c303294b6c875b720a</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>